--- a/data/trans_camb/IP16A08-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A08-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-2.10334012140815</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.3652903977531982</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.6108674864246152</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.9552258939292756</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-1.400142476283857</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-0.652814510303892</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-4.227722106897572</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.899816742764322</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.588503610716995</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-3.485035118716567</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-2.991099251493314</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-2.814822450511035</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>-0.3490027883512505</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.848795464170004</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.476662639585807</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>2.727552933686486</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.2409366469786919</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1.627021113237557</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.7788578435361898</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.1352654706496346</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.1853154086893753</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.2897814679256507</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.4681493554965304</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.2182739952784574</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.8372834913120197</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.728950892944502</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.9033847064478052</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.7717645406866095</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.7408429454740558</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.2881500297775229</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>2.020485434106653</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.8020216063390833</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1.741857206038801</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1298057808315635</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.820598740864131</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>0.2838339144660248</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.06952884333344435</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.3551211868087746</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.03903658566076877</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.3208518281260925</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0.004711922900293639</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-2.417971854216579</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.74737066903601</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.025783219478983</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.317200720807257</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-1.452313872712379</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-1.89548641008933</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>3.417303249427885</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.860034945194802</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.112105010162784</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.627002806161464</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>2.458993214519074</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>1.954677798181962</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>0.09644123886939561</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.02362454747822653</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.1653060242635374</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.01817121314104949</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1260553517096057</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.001851206838664597</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.5923448627806289</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.6580492660035585</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.6499102827410211</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.7663950557275823</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.447356830313722</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.5739975277618969</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>2.494639867471096</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>1.938508822388922</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>3.243426497059336</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>3.123083473539506</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.511346745334048</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.139642317838809</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>2.222446619871143</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.4023388245053737</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.01472864797993773</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.9149195863782846</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>1.066848451009724</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0.2216380640630226</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-1.262798838070617</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.119845726339655</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.736609657894609</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.726783547420997</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-1.12553624542518</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-1.798532591455115</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>6.12630152351597</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.275089081755449</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.392928135530441</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>4.053331757839889</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>3.218995661256293</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>2.286231809383112</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>0.8648584311703249</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.1565689458857757</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.008023122770933172</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.4983832987958622</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.4830388829380614</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.1003514630219781</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.392763497641355</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.8537957065794213</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.8855902667109309</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.7082237309241629</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.3797621407634215</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.5653376988041262</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>5.251786397760407</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>2.361930763757139</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>5.841554300856312</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>6.976629477149476</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>2.55706378781603</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1.880368848446123</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>1.501015450082786</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>1.129347836859544</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1.504122817392992</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.1451562151700777</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>1.493066302088587</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0.6675035189936226</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-1.525462582058817</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-1.89430876581872</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-2.351953995039434</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-4.067853379485052</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-1.184222049475866</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-1.864828824714349</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>5.331122548982684</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>4.316622562469745</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>7.240497180281413</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>3.111135106177958</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>4.533281736524295</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>2.733611850819202</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>1.056301540717606</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.7947498874945216</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.7459221456629164</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.07198563456649067</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.8826269139117635</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.3945950492422456</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,18 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-1</v>
+      </c>
       <c r="D26" s="6" t="inlineStr"/>
       <c r="E26" s="6" t="inlineStr"/>
       <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="n">
+        <v>-0.5290269957078276</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.6371894997892394</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1038,11 +1208,12 @@
       <c r="D27" s="6" t="inlineStr"/>
       <c r="E27" s="6" t="inlineStr"/>
       <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="n">
+        <v>7.982695906672195</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>5.882406238882858</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1226,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-0.1020673295040915</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-0.0869446813906969</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0.07362384056671424</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-0.08206982575492718</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.01649433005226839</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-0.08237248159498715</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1252,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-1.417480904166718</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-1.512579765431755</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-1.380957843783145</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-1.487008493920252</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-0.9806938255035501</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-1.087464910099113</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1278,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>1.215386501652178</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>1.591639928505331</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1.467240370643136</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>1.467738581285137</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.9472588851170548</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0.9833562654336057</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1304,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.03961666702132735</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.03374692478647205</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0.02990380802543669</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.03333431528653424</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.006543971192221305</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.0326805117201619</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1330,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.4425103537630508</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.4756655820615729</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.4240942109365827</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.474759150985858</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.3332049072536807</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.3588413352519824</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1356,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.6920253719245641</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.8804455364190521</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.8495325141119411</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.8397173011436796</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.4580871762837143</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.4923573737620881</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1384,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
